--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13495" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13495" uniqueCount="851">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -972,7 +972,7 @@
     <t>Laboratorieanalysresultat-Observation.varde</t>
   </si>
   <si>
-    <t xml:space="preserve">base64Binary
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
@@ -1373,10 +1373,6 @@
   </si>
   <si>
     <t>Origin.timeStamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Source attribute: timeStamp</t>
@@ -8620,7 +8616,7 @@
         <v>2</v>
       </c>
       <c r="B758" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="759">
@@ -8628,7 +8624,7 @@
         <v>4</v>
       </c>
       <c r="B759" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="760">
@@ -8644,7 +8640,7 @@
         <v>8</v>
       </c>
       <c r="B761" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="762">
@@ -8652,7 +8648,7 @@
         <v>10</v>
       </c>
       <c r="B762" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="763">
@@ -8706,7 +8702,7 @@
         <v>23</v>
       </c>
       <c r="B769" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="770">
@@ -8742,7 +8738,7 @@
         <v>31</v>
       </c>
       <c r="B774" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="775">
@@ -8782,7 +8778,7 @@
         <v>2</v>
       </c>
       <c r="B779" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="780">
@@ -8790,7 +8786,7 @@
         <v>4</v>
       </c>
       <c r="B780" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="781">
@@ -8806,7 +8802,7 @@
         <v>8</v>
       </c>
       <c r="B782" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="783">
@@ -8814,7 +8810,7 @@
         <v>10</v>
       </c>
       <c r="B783" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="784">
@@ -8868,7 +8864,7 @@
         <v>23</v>
       </c>
       <c r="B790" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="791">
@@ -8904,7 +8900,7 @@
         <v>31</v>
       </c>
       <c r="B795" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="796">
@@ -8944,7 +8940,7 @@
         <v>2</v>
       </c>
       <c r="B800" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="801">
@@ -8952,7 +8948,7 @@
         <v>4</v>
       </c>
       <c r="B801" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="802">
@@ -8968,7 +8964,7 @@
         <v>8</v>
       </c>
       <c r="B803" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="804">
@@ -8976,7 +8972,7 @@
         <v>10</v>
       </c>
       <c r="B804" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="805">
@@ -9030,7 +9026,7 @@
         <v>23</v>
       </c>
       <c r="B811" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="812">
@@ -9066,7 +9062,7 @@
         <v>31</v>
       </c>
       <c r="B816" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="817">
@@ -9106,7 +9102,7 @@
         <v>2</v>
       </c>
       <c r="B821" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="822">
@@ -9114,7 +9110,7 @@
         <v>4</v>
       </c>
       <c r="B822" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="823">
@@ -9130,7 +9126,7 @@
         <v>8</v>
       </c>
       <c r="B824" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="825">
@@ -9138,7 +9134,7 @@
         <v>10</v>
       </c>
       <c r="B825" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="826">
@@ -9192,7 +9188,7 @@
         <v>23</v>
       </c>
       <c r="B832" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="833">
@@ -9228,7 +9224,7 @@
         <v>31</v>
       </c>
       <c r="B837" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="838">
@@ -9268,7 +9264,7 @@
         <v>2</v>
       </c>
       <c r="B842" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="843">
@@ -9276,7 +9272,7 @@
         <v>4</v>
       </c>
       <c r="B843" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="844">
@@ -9292,7 +9288,7 @@
         <v>8</v>
       </c>
       <c r="B845" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="846">
@@ -9300,7 +9296,7 @@
         <v>10</v>
       </c>
       <c r="B846" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="847">
@@ -9354,7 +9350,7 @@
         <v>23</v>
       </c>
       <c r="B853" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="854">
@@ -9390,7 +9386,7 @@
         <v>31</v>
       </c>
       <c r="B858" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="859">
@@ -9430,7 +9426,7 @@
         <v>2</v>
       </c>
       <c r="B863" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="864">
@@ -9438,7 +9434,7 @@
         <v>4</v>
       </c>
       <c r="B864" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="865">
@@ -9454,7 +9450,7 @@
         <v>8</v>
       </c>
       <c r="B866" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="867">
@@ -9462,7 +9458,7 @@
         <v>10</v>
       </c>
       <c r="B867" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="868">
@@ -9516,7 +9512,7 @@
         <v>23</v>
       </c>
       <c r="B874" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="875">
@@ -9552,7 +9548,7 @@
         <v>31</v>
       </c>
       <c r="B879" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="880">
@@ -9592,7 +9588,7 @@
         <v>2</v>
       </c>
       <c r="B884" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="885">
@@ -9600,7 +9596,7 @@
         <v>4</v>
       </c>
       <c r="B885" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="886">
@@ -9616,7 +9612,7 @@
         <v>8</v>
       </c>
       <c r="B887" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="888">
@@ -9624,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="B888" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="889">
@@ -9678,7 +9674,7 @@
         <v>23</v>
       </c>
       <c r="B895" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="896">
@@ -9714,7 +9710,7 @@
         <v>31</v>
       </c>
       <c r="B900" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="901">
@@ -9754,7 +9750,7 @@
         <v>2</v>
       </c>
       <c r="B905" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="906">
@@ -9762,7 +9758,7 @@
         <v>4</v>
       </c>
       <c r="B906" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="907">
@@ -9778,7 +9774,7 @@
         <v>8</v>
       </c>
       <c r="B908" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="909">
@@ -9786,7 +9782,7 @@
         <v>10</v>
       </c>
       <c r="B909" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="910">
@@ -9840,7 +9836,7 @@
         <v>23</v>
       </c>
       <c r="B916" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="917">
@@ -9876,7 +9872,7 @@
         <v>31</v>
       </c>
       <c r="B921" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="922">
@@ -9916,7 +9912,7 @@
         <v>2</v>
       </c>
       <c r="B926" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="927">
@@ -9924,7 +9920,7 @@
         <v>4</v>
       </c>
       <c r="B927" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="928">
@@ -9940,7 +9936,7 @@
         <v>8</v>
       </c>
       <c r="B929" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="930">
@@ -9948,7 +9944,7 @@
         <v>10</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="931">
@@ -10002,7 +9998,7 @@
         <v>23</v>
       </c>
       <c r="B937" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="938">
@@ -10038,7 +10034,7 @@
         <v>31</v>
       </c>
       <c r="B942" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="943">
@@ -10078,7 +10074,7 @@
         <v>2</v>
       </c>
       <c r="B947" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="948">
@@ -10086,7 +10082,7 @@
         <v>4</v>
       </c>
       <c r="B948" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="949">
@@ -10102,7 +10098,7 @@
         <v>8</v>
       </c>
       <c r="B950" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="951">
@@ -10110,7 +10106,7 @@
         <v>10</v>
       </c>
       <c r="B951" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="952">
@@ -10164,7 +10160,7 @@
         <v>23</v>
       </c>
       <c r="B958" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="959">
@@ -10200,7 +10196,7 @@
         <v>31</v>
       </c>
       <c r="B963" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="964">
@@ -10240,7 +10236,7 @@
         <v>2</v>
       </c>
       <c r="B968" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="969">
@@ -10248,7 +10244,7 @@
         <v>4</v>
       </c>
       <c r="B969" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="970">
@@ -10264,7 +10260,7 @@
         <v>8</v>
       </c>
       <c r="B971" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="972">
@@ -10272,7 +10268,7 @@
         <v>10</v>
       </c>
       <c r="B972" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="973">
@@ -10326,7 +10322,7 @@
         <v>23</v>
       </c>
       <c r="B979" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="980">
@@ -10362,7 +10358,7 @@
         <v>31</v>
       </c>
       <c r="B984" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="985">
@@ -10402,7 +10398,7 @@
         <v>2</v>
       </c>
       <c r="B989" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="990">
@@ -10410,7 +10406,7 @@
         <v>4</v>
       </c>
       <c r="B990" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="991">
@@ -10426,7 +10422,7 @@
         <v>8</v>
       </c>
       <c r="B992" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="993">
@@ -10434,7 +10430,7 @@
         <v>10</v>
       </c>
       <c r="B993" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="994">
@@ -10488,7 +10484,7 @@
         <v>23</v>
       </c>
       <c r="B1000" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1001">
@@ -10524,7 +10520,7 @@
         <v>31</v>
       </c>
       <c r="B1005" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1006">
@@ -10564,7 +10560,7 @@
         <v>2</v>
       </c>
       <c r="B1010" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1011">
@@ -10572,7 +10568,7 @@
         <v>4</v>
       </c>
       <c r="B1011" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="1012">
@@ -10588,7 +10584,7 @@
         <v>8</v>
       </c>
       <c r="B1013" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1014">
@@ -10596,7 +10592,7 @@
         <v>10</v>
       </c>
       <c r="B1014" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1015">
@@ -10650,7 +10646,7 @@
         <v>23</v>
       </c>
       <c r="B1021" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="1022">
@@ -10686,7 +10682,7 @@
         <v>31</v>
       </c>
       <c r="B1026" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="1027">
@@ -10726,7 +10722,7 @@
         <v>2</v>
       </c>
       <c r="B1031" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1032">
@@ -10734,7 +10730,7 @@
         <v>4</v>
       </c>
       <c r="B1032" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="1033">
@@ -10750,7 +10746,7 @@
         <v>8</v>
       </c>
       <c r="B1034" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1035">
@@ -10758,7 +10754,7 @@
         <v>10</v>
       </c>
       <c r="B1035" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1036">
@@ -10812,7 +10808,7 @@
         <v>23</v>
       </c>
       <c r="B1042" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1043">
@@ -10848,7 +10844,7 @@
         <v>31</v>
       </c>
       <c r="B1047" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="1048">
@@ -10888,7 +10884,7 @@
         <v>2</v>
       </c>
       <c r="B1052" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1053">
@@ -10896,7 +10892,7 @@
         <v>4</v>
       </c>
       <c r="B1053" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1054">
@@ -10912,7 +10908,7 @@
         <v>8</v>
       </c>
       <c r="B1055" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1056">
@@ -10920,7 +10916,7 @@
         <v>10</v>
       </c>
       <c r="B1056" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1057">
@@ -10974,7 +10970,7 @@
         <v>23</v>
       </c>
       <c r="B1063" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1064">
@@ -11010,7 +11006,7 @@
         <v>31</v>
       </c>
       <c r="B1068" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1069">
@@ -11050,7 +11046,7 @@
         <v>2</v>
       </c>
       <c r="B1073" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1074">
@@ -11058,7 +11054,7 @@
         <v>4</v>
       </c>
       <c r="B1074" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1075">
@@ -11074,7 +11070,7 @@
         <v>8</v>
       </c>
       <c r="B1076" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1077">
@@ -11082,7 +11078,7 @@
         <v>10</v>
       </c>
       <c r="B1077" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1078">
@@ -11136,7 +11132,7 @@
         <v>23</v>
       </c>
       <c r="B1084" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1085">
@@ -11172,7 +11168,7 @@
         <v>31</v>
       </c>
       <c r="B1089" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1090">
@@ -11212,7 +11208,7 @@
         <v>2</v>
       </c>
       <c r="B1094" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1095">
@@ -11220,7 +11216,7 @@
         <v>4</v>
       </c>
       <c r="B1095" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1096">
@@ -11236,7 +11232,7 @@
         <v>8</v>
       </c>
       <c r="B1097" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1098">
@@ -11244,7 +11240,7 @@
         <v>10</v>
       </c>
       <c r="B1098" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1099">
@@ -11298,7 +11294,7 @@
         <v>23</v>
       </c>
       <c r="B1105" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1106">
@@ -11334,7 +11330,7 @@
         <v>31</v>
       </c>
       <c r="B1110" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1111">
@@ -11374,7 +11370,7 @@
         <v>2</v>
       </c>
       <c r="B1115" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1116">
@@ -11382,7 +11378,7 @@
         <v>4</v>
       </c>
       <c r="B1116" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1117">
@@ -11398,7 +11394,7 @@
         <v>8</v>
       </c>
       <c r="B1118" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1119">
@@ -11406,7 +11402,7 @@
         <v>10</v>
       </c>
       <c r="B1119" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1120">
@@ -11460,7 +11456,7 @@
         <v>23</v>
       </c>
       <c r="B1126" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1127">
@@ -11496,7 +11492,7 @@
         <v>31</v>
       </c>
       <c r="B1131" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1132">
@@ -11536,7 +11532,7 @@
         <v>2</v>
       </c>
       <c r="B1136" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1137">
@@ -11544,7 +11540,7 @@
         <v>4</v>
       </c>
       <c r="B1137" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1138">
@@ -11560,7 +11556,7 @@
         <v>8</v>
       </c>
       <c r="B1139" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1140">
@@ -11568,7 +11564,7 @@
         <v>10</v>
       </c>
       <c r="B1140" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1141">
@@ -11622,7 +11618,7 @@
         <v>23</v>
       </c>
       <c r="B1147" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1148">
@@ -11658,7 +11654,7 @@
         <v>31</v>
       </c>
       <c r="B1152" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1153">
@@ -11698,7 +11694,7 @@
         <v>2</v>
       </c>
       <c r="B1157" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1158">
@@ -11706,7 +11702,7 @@
         <v>4</v>
       </c>
       <c r="B1158" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1159">
@@ -11722,7 +11718,7 @@
         <v>8</v>
       </c>
       <c r="B1160" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1161">
@@ -11730,7 +11726,7 @@
         <v>10</v>
       </c>
       <c r="B1161" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1162">
@@ -11784,7 +11780,7 @@
         <v>23</v>
       </c>
       <c r="B1168" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1169">
@@ -11820,7 +11816,7 @@
         <v>31</v>
       </c>
       <c r="B1173" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1174">
@@ -11860,7 +11856,7 @@
         <v>2</v>
       </c>
       <c r="B1178" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1179">
@@ -11868,7 +11864,7 @@
         <v>4</v>
       </c>
       <c r="B1179" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="1180">
@@ -11884,7 +11880,7 @@
         <v>8</v>
       </c>
       <c r="B1181" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1182">
@@ -11892,7 +11888,7 @@
         <v>10</v>
       </c>
       <c r="B1182" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1183">
@@ -11946,7 +11942,7 @@
         <v>23</v>
       </c>
       <c r="B1189" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="1190">
@@ -11982,7 +11978,7 @@
         <v>31</v>
       </c>
       <c r="B1194" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="1195">
@@ -12022,7 +12018,7 @@
         <v>2</v>
       </c>
       <c r="B1199" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1200">
@@ -12030,7 +12026,7 @@
         <v>4</v>
       </c>
       <c r="B1200" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1201">
@@ -12046,7 +12042,7 @@
         <v>8</v>
       </c>
       <c r="B1202" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1203">
@@ -12054,7 +12050,7 @@
         <v>10</v>
       </c>
       <c r="B1203" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1204">
@@ -12108,7 +12104,7 @@
         <v>23</v>
       </c>
       <c r="B1210" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1211">
@@ -12144,7 +12140,7 @@
         <v>31</v>
       </c>
       <c r="B1215" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1216">
@@ -12184,7 +12180,7 @@
         <v>2</v>
       </c>
       <c r="B1220" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="1221">
@@ -12192,7 +12188,7 @@
         <v>4</v>
       </c>
       <c r="B1221" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1222">
@@ -12208,7 +12204,7 @@
         <v>8</v>
       </c>
       <c r="B1223" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1224">
@@ -12216,7 +12212,7 @@
         <v>10</v>
       </c>
       <c r="B1224" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1225">
@@ -12270,7 +12266,7 @@
         <v>23</v>
       </c>
       <c r="B1231" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1232">
@@ -12306,7 +12302,7 @@
         <v>31</v>
       </c>
       <c r="B1236" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1237">
@@ -12346,7 +12342,7 @@
         <v>2</v>
       </c>
       <c r="B1241" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1242">
@@ -12354,7 +12350,7 @@
         <v>4</v>
       </c>
       <c r="B1242" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1243">
@@ -12370,7 +12366,7 @@
         <v>8</v>
       </c>
       <c r="B1244" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="1245">
@@ -12378,7 +12374,7 @@
         <v>10</v>
       </c>
       <c r="B1245" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1246">
@@ -12432,7 +12428,7 @@
         <v>23</v>
       </c>
       <c r="B1252" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1253">
@@ -12468,7 +12464,7 @@
         <v>31</v>
       </c>
       <c r="B1257" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1258">
@@ -12508,7 +12504,7 @@
         <v>2</v>
       </c>
       <c r="B1262" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="1263">
@@ -12516,7 +12512,7 @@
         <v>4</v>
       </c>
       <c r="B1263" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="1264">
@@ -12532,7 +12528,7 @@
         <v>8</v>
       </c>
       <c r="B1265" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="1266">
@@ -12540,7 +12536,7 @@
         <v>10</v>
       </c>
       <c r="B1266" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="1267">
@@ -12594,7 +12590,7 @@
         <v>23</v>
       </c>
       <c r="B1273" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="1274">
@@ -12630,7 +12626,7 @@
         <v>31</v>
       </c>
       <c r="B1278" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="1279">
@@ -12670,7 +12666,7 @@
         <v>2</v>
       </c>
       <c r="B1283" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="1284">
@@ -12678,7 +12674,7 @@
         <v>4</v>
       </c>
       <c r="B1284" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1285">
@@ -12694,7 +12690,7 @@
         <v>8</v>
       </c>
       <c r="B1286" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="1287">
@@ -12702,7 +12698,7 @@
         <v>10</v>
       </c>
       <c r="B1287" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="1288">
@@ -12756,7 +12752,7 @@
         <v>23</v>
       </c>
       <c r="B1294" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="1295">
@@ -12792,7 +12788,7 @@
         <v>31</v>
       </c>
       <c r="B1299" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1300">
@@ -12832,7 +12828,7 @@
         <v>2</v>
       </c>
       <c r="B1304" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="1305">
@@ -12840,7 +12836,7 @@
         <v>4</v>
       </c>
       <c r="B1305" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1306">
@@ -12856,7 +12852,7 @@
         <v>8</v>
       </c>
       <c r="B1307" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="1308">
@@ -12864,7 +12860,7 @@
         <v>10</v>
       </c>
       <c r="B1308" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="1309">
@@ -12918,7 +12914,7 @@
         <v>23</v>
       </c>
       <c r="B1315" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1316">
@@ -12954,7 +12950,7 @@
         <v>31</v>
       </c>
       <c r="B1320" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1321">
@@ -12994,7 +12990,7 @@
         <v>2</v>
       </c>
       <c r="B1325" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="1326">
@@ -13002,7 +12998,7 @@
         <v>4</v>
       </c>
       <c r="B1326" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="1327">
@@ -13018,7 +13014,7 @@
         <v>8</v>
       </c>
       <c r="B1328" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="1329">
@@ -13026,7 +13022,7 @@
         <v>10</v>
       </c>
       <c r="B1329" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="1330">
@@ -13080,7 +13076,7 @@
         <v>23</v>
       </c>
       <c r="B1336" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="1337">
@@ -13116,7 +13112,7 @@
         <v>31</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="1342">
@@ -13156,7 +13152,7 @@
         <v>2</v>
       </c>
       <c r="B1346" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1347">
@@ -13164,7 +13160,7 @@
         <v>4</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1348">
@@ -13180,7 +13176,7 @@
         <v>8</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="1350">
@@ -13188,7 +13184,7 @@
         <v>10</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1351">
@@ -13242,7 +13238,7 @@
         <v>23</v>
       </c>
       <c r="B1357" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1358">
@@ -13278,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="B1362" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="1363">
@@ -13318,7 +13314,7 @@
         <v>2</v>
       </c>
       <c r="B1367" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1368">
@@ -13326,7 +13322,7 @@
         <v>4</v>
       </c>
       <c r="B1368" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1369">
@@ -13342,7 +13338,7 @@
         <v>8</v>
       </c>
       <c r="B1370" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1371">
@@ -13350,7 +13346,7 @@
         <v>10</v>
       </c>
       <c r="B1371" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="1372">
@@ -13404,7 +13400,7 @@
         <v>23</v>
       </c>
       <c r="B1378" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1379">
@@ -13440,7 +13436,7 @@
         <v>31</v>
       </c>
       <c r="B1383" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1384">
@@ -13480,7 +13476,7 @@
         <v>2</v>
       </c>
       <c r="B1388" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="1389">
@@ -13488,7 +13484,7 @@
         <v>4</v>
       </c>
       <c r="B1389" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1390">
@@ -13504,7 +13500,7 @@
         <v>8</v>
       </c>
       <c r="B1391" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1392">
@@ -13512,7 +13508,7 @@
         <v>10</v>
       </c>
       <c r="B1392" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="1393">
@@ -13566,7 +13562,7 @@
         <v>23</v>
       </c>
       <c r="B1399" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1400">
@@ -13602,7 +13598,7 @@
         <v>31</v>
       </c>
       <c r="B1404" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="1405">
@@ -13642,7 +13638,7 @@
         <v>2</v>
       </c>
       <c r="B1409" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1410">
@@ -13650,7 +13646,7 @@
         <v>4</v>
       </c>
       <c r="B1410" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1411">
@@ -13666,7 +13662,7 @@
         <v>8</v>
       </c>
       <c r="B1412" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1413">
@@ -13674,7 +13670,7 @@
         <v>10</v>
       </c>
       <c r="B1413" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1414">
@@ -13728,7 +13724,7 @@
         <v>23</v>
       </c>
       <c r="B1420" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1421">
@@ -13764,7 +13760,7 @@
         <v>31</v>
       </c>
       <c r="B1425" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1426">
@@ -13804,7 +13800,7 @@
         <v>2</v>
       </c>
       <c r="B1430" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1431">
@@ -13812,7 +13808,7 @@
         <v>4</v>
       </c>
       <c r="B1431" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1432">
@@ -13828,7 +13824,7 @@
         <v>8</v>
       </c>
       <c r="B1433" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1434">
@@ -13836,7 +13832,7 @@
         <v>10</v>
       </c>
       <c r="B1434" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1435">
@@ -13890,7 +13886,7 @@
         <v>23</v>
       </c>
       <c r="B1441" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="1442">
@@ -13926,7 +13922,7 @@
         <v>31</v>
       </c>
       <c r="B1446" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1447">
@@ -13966,7 +13962,7 @@
         <v>2</v>
       </c>
       <c r="B1451" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="1452">
@@ -13974,7 +13970,7 @@
         <v>4</v>
       </c>
       <c r="B1452" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="1453">
@@ -13990,7 +13986,7 @@
         <v>8</v>
       </c>
       <c r="B1454" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="1455">
@@ -13998,7 +13994,7 @@
         <v>10</v>
       </c>
       <c r="B1455" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="1456">
@@ -14052,7 +14048,7 @@
         <v>23</v>
       </c>
       <c r="B1462" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="1463">
@@ -14088,7 +14084,7 @@
         <v>31</v>
       </c>
       <c r="B1467" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="1468">
@@ -14128,7 +14124,7 @@
         <v>2</v>
       </c>
       <c r="B1472" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="1473">
@@ -14136,7 +14132,7 @@
         <v>4</v>
       </c>
       <c r="B1473" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1474">
@@ -14152,7 +14148,7 @@
         <v>8</v>
       </c>
       <c r="B1475" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="1476">
@@ -14160,7 +14156,7 @@
         <v>10</v>
       </c>
       <c r="B1476" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="1477">
@@ -14214,7 +14210,7 @@
         <v>23</v>
       </c>
       <c r="B1483" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="1484">
@@ -14250,7 +14246,7 @@
         <v>31</v>
       </c>
       <c r="B1488" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1489">
@@ -14290,7 +14286,7 @@
         <v>2</v>
       </c>
       <c r="B1493" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1494">
@@ -14298,7 +14294,7 @@
         <v>4</v>
       </c>
       <c r="B1494" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="1495">
@@ -14314,7 +14310,7 @@
         <v>8</v>
       </c>
       <c r="B1496" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1497">
@@ -14322,7 +14318,7 @@
         <v>10</v>
       </c>
       <c r="B1497" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1498">
@@ -14376,7 +14372,7 @@
         <v>23</v>
       </c>
       <c r="B1504" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="1505">
@@ -14412,7 +14408,7 @@
         <v>31</v>
       </c>
       <c r="B1509" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="1510">
@@ -14452,7 +14448,7 @@
         <v>2</v>
       </c>
       <c r="B1514" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1515">
@@ -14460,7 +14456,7 @@
         <v>4</v>
       </c>
       <c r="B1515" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="1516">
@@ -14476,7 +14472,7 @@
         <v>8</v>
       </c>
       <c r="B1517" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="1518">
@@ -14484,7 +14480,7 @@
         <v>10</v>
       </c>
       <c r="B1518" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="1519">
@@ -14538,7 +14534,7 @@
         <v>23</v>
       </c>
       <c r="B1525" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="1526">
@@ -14574,7 +14570,7 @@
         <v>31</v>
       </c>
       <c r="B1530" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="1531">
@@ -14614,7 +14610,7 @@
         <v>2</v>
       </c>
       <c r="B1535" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="1536">
@@ -14622,7 +14618,7 @@
         <v>4</v>
       </c>
       <c r="B1536" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="1537">
@@ -14638,7 +14634,7 @@
         <v>8</v>
       </c>
       <c r="B1538" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="1539">
@@ -14646,7 +14642,7 @@
         <v>10</v>
       </c>
       <c r="B1539" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="1540">
@@ -14700,7 +14696,7 @@
         <v>23</v>
       </c>
       <c r="B1546" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="1547">
@@ -14736,7 +14732,7 @@
         <v>31</v>
       </c>
       <c r="B1551" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="1552">
@@ -14776,7 +14772,7 @@
         <v>2</v>
       </c>
       <c r="B1556" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1557">
@@ -14784,7 +14780,7 @@
         <v>4</v>
       </c>
       <c r="B1557" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="1558">
@@ -14800,7 +14796,7 @@
         <v>8</v>
       </c>
       <c r="B1559" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="1560">
@@ -14808,7 +14804,7 @@
         <v>10</v>
       </c>
       <c r="B1560" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="1561">
@@ -14862,7 +14858,7 @@
         <v>23</v>
       </c>
       <c r="B1567" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="1568">
@@ -14898,7 +14894,7 @@
         <v>31</v>
       </c>
       <c r="B1572" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="1573">
@@ -14938,7 +14934,7 @@
         <v>2</v>
       </c>
       <c r="B1577" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="1578">
@@ -14946,7 +14942,7 @@
         <v>4</v>
       </c>
       <c r="B1578" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="1579">
@@ -14962,7 +14958,7 @@
         <v>8</v>
       </c>
       <c r="B1580" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="1581">
@@ -14970,7 +14966,7 @@
         <v>10</v>
       </c>
       <c r="B1581" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="1582">
@@ -15024,7 +15020,7 @@
         <v>23</v>
       </c>
       <c r="B1588" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="1589">
@@ -15060,7 +15056,7 @@
         <v>31</v>
       </c>
       <c r="B1593" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="1594">
@@ -15100,7 +15096,7 @@
         <v>2</v>
       </c>
       <c r="B1598" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="1599">
@@ -15108,7 +15104,7 @@
         <v>4</v>
       </c>
       <c r="B1599" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="1600">
@@ -15124,7 +15120,7 @@
         <v>8</v>
       </c>
       <c r="B1601" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="1602">
@@ -15132,7 +15128,7 @@
         <v>10</v>
       </c>
       <c r="B1602" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="1603">
@@ -15186,7 +15182,7 @@
         <v>23</v>
       </c>
       <c r="B1609" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="1610">
@@ -15222,7 +15218,7 @@
         <v>31</v>
       </c>
       <c r="B1614" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="1615">
@@ -15262,7 +15258,7 @@
         <v>2</v>
       </c>
       <c r="B1619" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="1620">
@@ -15270,7 +15266,7 @@
         <v>4</v>
       </c>
       <c r="B1620" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="1621">
@@ -15286,7 +15282,7 @@
         <v>8</v>
       </c>
       <c r="B1622" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="1623">
@@ -15294,7 +15290,7 @@
         <v>10</v>
       </c>
       <c r="B1623" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="1624">
@@ -15348,7 +15344,7 @@
         <v>23</v>
       </c>
       <c r="B1630" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="1631">
@@ -15384,7 +15380,7 @@
         <v>31</v>
       </c>
       <c r="B1635" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="1636">
@@ -15424,7 +15420,7 @@
         <v>2</v>
       </c>
       <c r="B1640" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="1641">
@@ -15432,7 +15428,7 @@
         <v>4</v>
       </c>
       <c r="B1641" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="1642">
@@ -15448,7 +15444,7 @@
         <v>8</v>
       </c>
       <c r="B1643" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="1644">
@@ -15456,7 +15452,7 @@
         <v>10</v>
       </c>
       <c r="B1644" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="1645">
@@ -15510,7 +15506,7 @@
         <v>23</v>
       </c>
       <c r="B1651" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="1652">
@@ -15546,7 +15542,7 @@
         <v>31</v>
       </c>
       <c r="B1656" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="1657">
@@ -15586,7 +15582,7 @@
         <v>2</v>
       </c>
       <c r="B1661" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="1662">
@@ -15594,7 +15590,7 @@
         <v>4</v>
       </c>
       <c r="B1662" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="1663">
@@ -15610,7 +15606,7 @@
         <v>8</v>
       </c>
       <c r="B1664" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="1665">
@@ -15618,7 +15614,7 @@
         <v>10</v>
       </c>
       <c r="B1665" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="1666">
@@ -15672,7 +15668,7 @@
         <v>23</v>
       </c>
       <c r="B1672" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="1673">
@@ -15708,7 +15704,7 @@
         <v>31</v>
       </c>
       <c r="B1677" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="1678">
@@ -15748,7 +15744,7 @@
         <v>2</v>
       </c>
       <c r="B1682" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1683">
@@ -15756,7 +15752,7 @@
         <v>4</v>
       </c>
       <c r="B1683" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1684">
@@ -15772,7 +15768,7 @@
         <v>8</v>
       </c>
       <c r="B1685" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1686">
@@ -15780,7 +15776,7 @@
         <v>10</v>
       </c>
       <c r="B1686" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="1687">
@@ -15834,7 +15830,7 @@
         <v>23</v>
       </c>
       <c r="B1693" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="1694">
@@ -15870,7 +15866,7 @@
         <v>31</v>
       </c>
       <c r="B1698" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1699">
@@ -15910,7 +15906,7 @@
         <v>2</v>
       </c>
       <c r="B1703" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="1704">
@@ -15918,7 +15914,7 @@
         <v>4</v>
       </c>
       <c r="B1704" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="1705">
@@ -15934,7 +15930,7 @@
         <v>8</v>
       </c>
       <c r="B1706" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="1707">
@@ -15942,7 +15938,7 @@
         <v>10</v>
       </c>
       <c r="B1707" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="1708">
@@ -15996,7 +15992,7 @@
         <v>23</v>
       </c>
       <c r="B1714" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="1715">
@@ -16032,7 +16028,7 @@
         <v>31</v>
       </c>
       <c r="B1719" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="1720">
@@ -16072,7 +16068,7 @@
         <v>2</v>
       </c>
       <c r="B1724" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="1725">
@@ -16080,7 +16076,7 @@
         <v>4</v>
       </c>
       <c r="B1725" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="1726">
@@ -16096,7 +16092,7 @@
         <v>8</v>
       </c>
       <c r="B1727" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="1728">
@@ -16104,7 +16100,7 @@
         <v>10</v>
       </c>
       <c r="B1728" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="1729">
@@ -16158,7 +16154,7 @@
         <v>23</v>
       </c>
       <c r="B1735" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="1736">
@@ -16194,7 +16190,7 @@
         <v>31</v>
       </c>
       <c r="B1740" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="1741">
@@ -16234,7 +16230,7 @@
         <v>2</v>
       </c>
       <c r="B1745" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="1746">
@@ -16242,7 +16238,7 @@
         <v>4</v>
       </c>
       <c r="B1746" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="1747">
@@ -16258,7 +16254,7 @@
         <v>8</v>
       </c>
       <c r="B1748" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="1749">
@@ -16266,7 +16262,7 @@
         <v>10</v>
       </c>
       <c r="B1749" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="1750">
@@ -16320,7 +16316,7 @@
         <v>23</v>
       </c>
       <c r="B1756" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="1757">
@@ -16356,7 +16352,7 @@
         <v>31</v>
       </c>
       <c r="B1761" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="1762">
@@ -16396,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="B1766" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="1767">
@@ -16404,7 +16400,7 @@
         <v>4</v>
       </c>
       <c r="B1767" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="1768">
@@ -16420,7 +16416,7 @@
         <v>8</v>
       </c>
       <c r="B1769" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="1770">
@@ -16428,7 +16424,7 @@
         <v>10</v>
       </c>
       <c r="B1770" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="1771">
@@ -16482,7 +16478,7 @@
         <v>23</v>
       </c>
       <c r="B1777" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="1778">
@@ -16518,7 +16514,7 @@
         <v>31</v>
       </c>
       <c r="B1782" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="1783">
@@ -16558,7 +16554,7 @@
         <v>2</v>
       </c>
       <c r="B1787" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="1788">
@@ -16566,7 +16562,7 @@
         <v>4</v>
       </c>
       <c r="B1788" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="1789">
@@ -16582,7 +16578,7 @@
         <v>8</v>
       </c>
       <c r="B1790" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="1791">
@@ -16590,7 +16586,7 @@
         <v>10</v>
       </c>
       <c r="B1791" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="1792">
@@ -16644,7 +16640,7 @@
         <v>23</v>
       </c>
       <c r="B1798" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="1799">
@@ -16680,7 +16676,7 @@
         <v>31</v>
       </c>
       <c r="B1803" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="1804">
@@ -16720,7 +16716,7 @@
         <v>2</v>
       </c>
       <c r="B1808" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="1809">
@@ -16728,7 +16724,7 @@
         <v>4</v>
       </c>
       <c r="B1809" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="1810">
@@ -16744,7 +16740,7 @@
         <v>8</v>
       </c>
       <c r="B1811" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="1812">
@@ -16752,7 +16748,7 @@
         <v>10</v>
       </c>
       <c r="B1812" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="1813">
@@ -16806,7 +16802,7 @@
         <v>23</v>
       </c>
       <c r="B1819" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="1820">
@@ -16842,7 +16838,7 @@
         <v>31</v>
       </c>
       <c r="B1824" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="1825">
@@ -16882,7 +16878,7 @@
         <v>2</v>
       </c>
       <c r="B1829" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="1830">
@@ -16890,7 +16886,7 @@
         <v>4</v>
       </c>
       <c r="B1830" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="1831">
@@ -16906,7 +16902,7 @@
         <v>8</v>
       </c>
       <c r="B1832" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="1833">
@@ -16914,7 +16910,7 @@
         <v>10</v>
       </c>
       <c r="B1833" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="1834">
@@ -16968,7 +16964,7 @@
         <v>23</v>
       </c>
       <c r="B1840" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="1841">
@@ -17004,7 +17000,7 @@
         <v>31</v>
       </c>
       <c r="B1845" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="1846">
@@ -17044,7 +17040,7 @@
         <v>2</v>
       </c>
       <c r="B1850" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="1851">
@@ -17052,7 +17048,7 @@
         <v>4</v>
       </c>
       <c r="B1851" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="1852">
@@ -17068,7 +17064,7 @@
         <v>8</v>
       </c>
       <c r="B1853" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="1854">
@@ -17076,7 +17072,7 @@
         <v>10</v>
       </c>
       <c r="B1854" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="1855">
@@ -17130,7 +17126,7 @@
         <v>23</v>
       </c>
       <c r="B1861" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="1862">
@@ -17166,7 +17162,7 @@
         <v>31</v>
       </c>
       <c r="B1866" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="1867">
@@ -31598,13 +31594,13 @@
         <v>22</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="N140" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -31675,10 +31671,10 @@
         <v>434</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -31701,13 +31697,13 @@
         <v>22</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
@@ -31758,7 +31754,7 @@
         <v>22</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>74</v>
@@ -31775,13 +31771,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -31807,10 +31803,10 @@
         <v>22</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -31878,13 +31874,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -31910,10 +31906,10 @@
         <v>76</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -31981,13 +31977,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -32010,7 +32006,7 @@
         <v>22</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M144" t="s" s="2">
         <v>394</v>
@@ -32067,7 +32063,7 @@
         <v>22</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>74</v>
@@ -32084,13 +32080,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -32170,7 +32166,7 @@
         <v>22</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>74</v>
@@ -32187,13 +32183,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -32219,10 +32215,10 @@
         <v>76</v>
       </c>
       <c r="M146" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -32290,13 +32286,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B147" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C147" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -32376,7 +32372,7 @@
         <v>22</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>74</v>
@@ -32393,13 +32389,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -32479,7 +32475,7 @@
         <v>22</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>74</v>
@@ -32496,13 +32492,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -32525,13 +32521,13 @@
         <v>22</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M149" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="N149" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -32582,7 +32578,7 @@
         <v>22</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>79</v>
@@ -32599,13 +32595,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -32631,10 +32627,10 @@
         <v>76</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -32702,13 +32698,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B151" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C151" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -32731,7 +32727,7 @@
         <v>22</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>112</v>
@@ -32788,7 +32784,7 @@
         <v>22</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>79</v>
@@ -32805,13 +32801,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -32834,7 +32830,7 @@
         <v>22</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M152" t="s" s="2">
         <v>93</v>
@@ -32891,7 +32887,7 @@
         <v>22</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>74</v>
@@ -32908,13 +32904,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -32937,13 +32933,13 @@
         <v>22</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M153" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="N153" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -32994,7 +32990,7 @@
         <v>22</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>74</v>
@@ -33011,13 +33007,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -33043,10 +33039,10 @@
         <v>76</v>
       </c>
       <c r="M154" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -33114,13 +33110,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B155" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C155" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -33200,7 +33196,7 @@
         <v>22</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>74</v>
@@ -33217,13 +33213,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -33303,7 +33299,7 @@
         <v>22</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>74</v>
@@ -33320,13 +33316,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -33352,10 +33348,10 @@
         <v>279</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -33406,7 +33402,7 @@
         <v>22</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>74</v>
@@ -33423,13 +33419,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -33455,10 +33451,10 @@
         <v>95</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
@@ -33509,7 +33505,7 @@
         <v>22</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>74</v>
@@ -33526,13 +33522,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -33558,10 +33554,10 @@
         <v>375</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
@@ -33612,7 +33608,7 @@
         <v>22</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>79</v>
@@ -33629,13 +33625,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -33661,10 +33657,10 @@
         <v>76</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -33732,13 +33728,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -33761,13 +33757,13 @@
         <v>22</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -33818,7 +33814,7 @@
         <v>22</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>79</v>
@@ -33835,13 +33831,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -33864,7 +33860,7 @@
         <v>22</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M162" t="s" s="2">
         <v>93</v>
@@ -33921,7 +33917,7 @@
         <v>22</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>74</v>
@@ -33938,13 +33934,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -33967,13 +33963,13 @@
         <v>22</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -34024,7 +34020,7 @@
         <v>22</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>74</v>
@@ -34041,13 +34037,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -34073,10 +34069,10 @@
         <v>76</v>
       </c>
       <c r="M164" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -34144,13 +34140,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -34173,7 +34169,7 @@
         <v>22</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M165" t="s" s="2">
         <v>151</v>
@@ -34230,7 +34226,7 @@
         <v>22</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>74</v>
@@ -34247,13 +34243,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -34279,10 +34275,10 @@
         <v>76</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -34350,13 +34346,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -34382,10 +34378,10 @@
         <v>126</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -34436,7 +34432,7 @@
         <v>22</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>74</v>
@@ -34453,13 +34449,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -34485,10 +34481,10 @@
         <v>76</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -34556,13 +34552,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -34585,7 +34581,7 @@
         <v>22</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>89</v>
@@ -34642,7 +34638,7 @@
         <v>22</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>74</v>
@@ -34659,13 +34655,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -34688,13 +34684,13 @@
         <v>22</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M170" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="N170" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -34745,7 +34741,7 @@
         <v>22</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>74</v>
@@ -34762,13 +34758,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -34791,13 +34787,13 @@
         <v>22</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M171" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="N171" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -34848,7 +34844,7 @@
         <v>22</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>74</v>
@@ -34865,13 +34861,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -34951,7 +34947,7 @@
         <v>22</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>74</v>
@@ -34968,13 +34964,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -34997,13 +34993,13 @@
         <v>22</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M173" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="N173" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
@@ -35054,7 +35050,7 @@
         <v>22</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>74</v>
@@ -35071,13 +35067,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -35100,13 +35096,13 @@
         <v>22</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M174" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="N174" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -35157,7 +35153,7 @@
         <v>22</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>74</v>
@@ -35174,13 +35170,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -35206,10 +35202,10 @@
         <v>76</v>
       </c>
       <c r="M175" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
@@ -35277,13 +35273,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B176" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -35363,7 +35359,7 @@
         <v>22</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>74</v>
@@ -35380,13 +35376,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -35412,10 +35408,10 @@
         <v>114</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
@@ -35466,7 +35462,7 @@
         <v>22</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>79</v>
@@ -35483,13 +35479,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -35515,10 +35511,10 @@
         <v>279</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
@@ -35569,7 +35565,7 @@
         <v>22</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>79</v>
@@ -35586,13 +35582,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -35618,10 +35614,10 @@
         <v>114</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
@@ -35672,7 +35668,7 @@
         <v>22</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>74</v>
@@ -35689,13 +35685,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -35775,7 +35771,7 @@
         <v>22</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>74</v>
@@ -35792,13 +35788,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -35821,13 +35817,13 @@
         <v>22</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M181" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="N181" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
@@ -35878,7 +35874,7 @@
         <v>22</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>74</v>
@@ -35895,13 +35891,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -35924,7 +35920,7 @@
         <v>22</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M182" t="s" s="2">
         <v>299</v>
@@ -35981,7 +35977,7 @@
         <v>22</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>74</v>
@@ -35998,13 +35994,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -36084,7 +36080,7 @@
         <v>22</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>74</v>
@@ -36101,13 +36097,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -36133,10 +36129,10 @@
         <v>76</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
@@ -36204,13 +36200,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -36236,10 +36232,10 @@
         <v>88</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
@@ -36290,7 +36286,7 @@
         <v>22</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>74</v>
@@ -36307,13 +36303,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -36339,10 +36335,10 @@
         <v>76</v>
       </c>
       <c r="M186" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N186" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -36410,13 +36406,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B187" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C187" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -36496,7 +36492,7 @@
         <v>22</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>74</v>
@@ -36513,13 +36509,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -36599,7 +36595,7 @@
         <v>22</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>79</v>
@@ -36616,13 +36612,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -36648,10 +36644,10 @@
         <v>298</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
@@ -36702,7 +36698,7 @@
         <v>22</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>74</v>
@@ -36719,13 +36715,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -36751,10 +36747,10 @@
         <v>76</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
@@ -36822,13 +36818,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -36854,10 +36850,10 @@
         <v>88</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
@@ -36908,7 +36904,7 @@
         <v>22</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>74</v>
@@ -36925,13 +36921,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -36957,10 +36953,10 @@
         <v>76</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -37028,13 +37024,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -37060,10 +37056,10 @@
         <v>88</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -37114,7 +37110,7 @@
         <v>22</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>74</v>
@@ -37131,13 +37127,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -37163,10 +37159,10 @@
         <v>76</v>
       </c>
       <c r="M194" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
@@ -37234,13 +37230,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -37320,7 +37316,7 @@
         <v>22</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>79</v>
@@ -37337,13 +37333,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -37366,7 +37362,7 @@
         <v>22</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M196" t="s" s="2">
         <v>280</v>
@@ -37423,7 +37419,7 @@
         <v>22</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>79</v>
@@ -37440,13 +37436,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -37526,7 +37522,7 @@
         <v>22</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>74</v>
@@ -37543,13 +37539,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -37629,7 +37625,7 @@
         <v>22</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>79</v>
@@ -37646,13 +37642,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -37678,10 +37674,10 @@
         <v>76</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
@@ -37749,13 +37745,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -37781,10 +37777,10 @@
         <v>88</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
@@ -37835,7 +37831,7 @@
         <v>22</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>74</v>
@@ -37852,13 +37848,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -37884,10 +37880,10 @@
         <v>76</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
@@ -37955,13 +37951,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -37984,13 +37980,13 @@
         <v>22</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
@@ -38041,7 +38037,7 @@
         <v>22</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>74</v>
@@ -38058,13 +38054,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -38144,7 +38140,7 @@
         <v>22</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>74</v>
@@ -38161,13 +38157,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -38193,10 +38189,10 @@
         <v>92</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
@@ -38247,7 +38243,7 @@
         <v>22</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>74</v>
@@ -38264,13 +38260,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -38350,7 +38346,7 @@
         <v>22</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>74</v>
@@ -38367,13 +38363,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -38453,7 +38449,7 @@
         <v>22</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>74</v>
@@ -38470,13 +38466,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -38502,10 +38498,10 @@
         <v>76</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -38573,13 +38569,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -38602,13 +38598,13 @@
         <v>22</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -38659,7 +38655,7 @@
         <v>22</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>74</v>
@@ -38676,13 +38672,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -38705,13 +38701,13 @@
         <v>22</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
@@ -38762,7 +38758,7 @@
         <v>22</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>74</v>
@@ -38779,13 +38775,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -38811,10 +38807,10 @@
         <v>76</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" s="2"/>
@@ -38882,13 +38878,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -38914,10 +38910,10 @@
         <v>391</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" s="2"/>
@@ -38968,7 +38964,7 @@
         <v>22</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>74</v>
@@ -38985,13 +38981,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -39071,7 +39067,7 @@
         <v>22</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>74</v>
@@ -39088,13 +39084,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -39120,10 +39116,10 @@
         <v>76</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -39191,13 +39187,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -39220,13 +39216,13 @@
         <v>22</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" s="2"/>
@@ -39277,7 +39273,7 @@
         <v>22</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>74</v>
@@ -39294,13 +39290,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -39323,13 +39319,13 @@
         <v>22</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
@@ -39380,7 +39376,7 @@
         <v>22</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>74</v>
@@ -39397,13 +39393,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -39429,10 +39425,10 @@
         <v>76</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" s="2"/>
@@ -39500,13 +39496,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -39532,10 +39528,10 @@
         <v>331</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
@@ -39586,7 +39582,7 @@
         <v>22</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>74</v>
@@ -39603,13 +39599,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -39632,7 +39628,7 @@
         <v>22</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M218" t="s" s="2">
         <v>320</v>
@@ -39689,7 +39685,7 @@
         <v>22</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>74</v>
@@ -39706,13 +39702,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -39738,10 +39734,10 @@
         <v>76</v>
       </c>
       <c r="M219" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N219" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -39809,13 +39805,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -39895,7 +39891,7 @@
         <v>22</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>74</v>
@@ -39912,13 +39908,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -39944,10 +39940,10 @@
         <v>76</v>
       </c>
       <c r="M221" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N221" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" s="2"/>
@@ -40015,13 +40011,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -40047,10 +40043,10 @@
         <v>204</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" s="2"/>
@@ -40101,7 +40097,7 @@
         <v>22</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>74</v>
@@ -40118,13 +40114,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -40150,10 +40146,10 @@
         <v>417</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -40204,7 +40200,7 @@
         <v>22</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>74</v>
@@ -40221,13 +40217,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -40307,7 +40303,7 @@
         <v>22</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>74</v>
@@ -40324,13 +40320,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -40410,7 +40406,7 @@
         <v>22</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>74</v>
@@ -40427,13 +40423,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -40459,10 +40455,10 @@
         <v>126</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" s="2"/>
@@ -40513,7 +40509,7 @@
         <v>22</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>74</v>
@@ -40530,13 +40526,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -40562,10 +40558,10 @@
         <v>76</v>
       </c>
       <c r="M227" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N227" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
@@ -40633,13 +40629,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -40665,10 +40661,10 @@
         <v>111</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" s="2"/>
@@ -40719,7 +40715,7 @@
         <v>22</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>79</v>
@@ -40736,13 +40732,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -40768,10 +40764,10 @@
         <v>279</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="O229" s="2"/>
       <c r="P229" s="2"/>
@@ -40822,7 +40818,7 @@
         <v>22</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>79</v>
@@ -40839,13 +40835,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -40868,13 +40864,13 @@
         <v>22</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M230" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="N230" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" s="2"/>
@@ -40925,7 +40921,7 @@
         <v>22</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>74</v>
@@ -40942,13 +40938,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -40974,10 +40970,10 @@
         <v>92</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
@@ -41028,7 +41024,7 @@
         <v>22</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>74</v>
@@ -41045,13 +41041,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -41077,10 +41073,10 @@
         <v>114</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" s="2"/>
@@ -41131,7 +41127,7 @@
         <v>22</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>74</v>
@@ -41148,13 +41144,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -41180,10 +41176,10 @@
         <v>92</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
@@ -41234,7 +41230,7 @@
         <v>22</v>
       </c>
       <c r="AG233" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AH233" t="s" s="2">
         <v>74</v>
@@ -41251,13 +41247,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -41283,10 +41279,10 @@
         <v>92</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" s="2"/>
@@ -41337,7 +41333,7 @@
         <v>22</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>74</v>
@@ -41354,13 +41350,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -41440,7 +41436,7 @@
         <v>22</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>74</v>
@@ -41457,13 +41453,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -41543,7 +41539,7 @@
         <v>22</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>74</v>
@@ -41560,13 +41556,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -41592,10 +41588,10 @@
         <v>76</v>
       </c>
       <c r="M237" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N237" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" s="2"/>
@@ -41663,13 +41659,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -41749,7 +41745,7 @@
         <v>22</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>74</v>
@@ -41766,13 +41762,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -41798,10 +41794,10 @@
         <v>263</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" s="2"/>
@@ -41852,7 +41848,7 @@
         <v>22</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AH239" t="s" s="2">
         <v>74</v>
@@ -41869,13 +41865,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -41901,10 +41897,10 @@
         <v>76</v>
       </c>
       <c r="M240" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N240" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" s="2"/>
@@ -41972,13 +41968,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -42058,7 +42054,7 @@
         <v>22</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>74</v>
@@ -42075,13 +42071,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -42104,13 +42100,13 @@
         <v>22</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
@@ -42161,7 +42157,7 @@
         <v>22</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>74</v>
@@ -42178,13 +42174,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -42210,10 +42206,10 @@
         <v>411</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -42264,7 +42260,7 @@
         <v>22</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>74</v>
@@ -42281,13 +42277,13 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -42367,7 +42363,7 @@
         <v>22</v>
       </c>
       <c r="AG244" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AH244" t="s" s="2">
         <v>74</v>
@@ -42384,13 +42380,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -42470,7 +42466,7 @@
         <v>22</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>74</v>
@@ -42487,13 +42483,13 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -42519,10 +42515,10 @@
         <v>263</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" s="2"/>
@@ -42573,7 +42569,7 @@
         <v>22</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>74</v>
@@ -42590,13 +42586,13 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -42619,7 +42615,7 @@
         <v>22</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M247" t="s" s="2">
         <v>151</v>
@@ -42676,7 +42672,7 @@
         <v>22</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>74</v>
@@ -42693,13 +42689,13 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" t="s" s="2">
@@ -42722,7 +42718,7 @@
         <v>22</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="M248" t="s" s="2">
         <v>151</v>
@@ -42779,7 +42775,7 @@
         <v>22</v>
       </c>
       <c r="AG248" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AH248" t="s" s="2">
         <v>74</v>
@@ -42796,13 +42792,13 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
@@ -42882,7 +42878,7 @@
         <v>22</v>
       </c>
       <c r="AG249" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AH249" t="s" s="2">
         <v>74</v>
@@ -42899,13 +42895,13 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -42931,10 +42927,10 @@
         <v>76</v>
       </c>
       <c r="M250" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N250" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N250" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O250" s="2"/>
       <c r="P250" s="2"/>
@@ -43002,13 +42998,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
@@ -43034,10 +43030,10 @@
         <v>126</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="O251" s="2"/>
       <c r="P251" s="2"/>
@@ -43088,7 +43084,7 @@
         <v>22</v>
       </c>
       <c r="AG251" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>74</v>
@@ -43105,13 +43101,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -43191,7 +43187,7 @@
         <v>22</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>74</v>
@@ -43208,13 +43204,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -43240,10 +43236,10 @@
         <v>76</v>
       </c>
       <c r="M253" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N253" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="O253" s="2"/>
       <c r="P253" s="2"/>
@@ -43311,13 +43307,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -43343,10 +43339,10 @@
         <v>263</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O254" s="2"/>
       <c r="P254" s="2"/>
@@ -43397,7 +43393,7 @@
         <v>22</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>74</v>
@@ -43414,13 +43410,13 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -43500,7 +43496,7 @@
         <v>22</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AH255" t="s" s="2">
         <v>74</v>
@@ -43517,13 +43513,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -43546,7 +43542,7 @@
         <v>22</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="M256" t="s" s="2">
         <v>130</v>
@@ -43603,7 +43599,7 @@
         <v>22</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>74</v>
@@ -43620,13 +43616,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -43652,10 +43648,10 @@
         <v>76</v>
       </c>
       <c r="M257" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N257" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="N257" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" s="2"/>
@@ -43723,13 +43719,13 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" t="s" s="2">
@@ -43809,7 +43805,7 @@
         <v>22</v>
       </c>
       <c r="AG258" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AH258" t="s" s="2">
         <v>74</v>
@@ -43826,13 +43822,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -43912,7 +43908,7 @@
         <v>22</v>
       </c>
       <c r="AG259" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AH259" t="s" s="2">
         <v>74</v>
@@ -43929,13 +43925,13 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" t="s" s="2">
@@ -43961,10 +43957,10 @@
         <v>76</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N260" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O260" s="2"/>
       <c r="P260" s="2"/>
@@ -44032,13 +44028,13 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" t="s" s="2">
@@ -44064,10 +44060,10 @@
         <v>399</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N261" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="O261" s="2"/>
       <c r="P261" s="2"/>
@@ -44118,7 +44114,7 @@
         <v>22</v>
       </c>
       <c r="AG261" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AH261" t="s" s="2">
         <v>74</v>
@@ -44135,13 +44131,13 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" t="s" s="2">
@@ -44167,10 +44163,10 @@
         <v>76</v>
       </c>
       <c r="M262" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="N262" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="N262" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="O262" s="2"/>
       <c r="P262" s="2"/>
@@ -44238,13 +44234,13 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" t="s" s="2">
@@ -44267,13 +44263,13 @@
         <v>22</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" s="2"/>
@@ -44324,7 +44320,7 @@
         <v>22</v>
       </c>
       <c r="AG263" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AH263" t="s" s="2">
         <v>74</v>
@@ -44341,13 +44337,13 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" t="s" s="2">
@@ -44427,7 +44423,7 @@
         <v>22</v>
       </c>
       <c r="AG264" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AH264" t="s" s="2">
         <v>74</v>
@@ -44444,13 +44440,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" t="s" s="2">
@@ -44476,10 +44472,10 @@
         <v>76</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O265" s="2"/>
       <c r="P265" s="2"/>
@@ -44547,13 +44543,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" t="s" s="2">
@@ -44576,13 +44572,13 @@
         <v>22</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="O266" s="2"/>
       <c r="P266" s="2"/>
@@ -44633,7 +44629,7 @@
         <v>22</v>
       </c>
       <c r="AG266" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AH266" t="s" s="2">
         <v>74</v>
@@ -44650,13 +44646,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" t="s" s="2">
@@ -44679,13 +44675,13 @@
         <v>22</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="O267" s="2"/>
       <c r="P267" s="2"/>
@@ -44736,7 +44732,7 @@
         <v>22</v>
       </c>
       <c r="AG267" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AH267" t="s" s="2">
         <v>74</v>
@@ -44753,13 +44749,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
@@ -44782,13 +44778,13 @@
         <v>22</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" s="2"/>
@@ -44839,7 +44835,7 @@
         <v>22</v>
       </c>
       <c r="AG268" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AH268" t="s" s="2">
         <v>74</v>
@@ -44856,13 +44852,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -44885,13 +44881,13 @@
         <v>22</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O269" s="2"/>
       <c r="P269" s="2"/>
@@ -44942,7 +44938,7 @@
         <v>22</v>
       </c>
       <c r="AG269" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AH269" t="s" s="2">
         <v>74</v>
@@ -44959,13 +44955,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -44988,13 +44984,13 @@
         <v>22</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O270" s="2"/>
       <c r="P270" s="2"/>
@@ -45045,7 +45041,7 @@
         <v>22</v>
       </c>
       <c r="AG270" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AH270" t="s" s="2">
         <v>74</v>
@@ -45062,13 +45058,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -45091,13 +45087,13 @@
         <v>22</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="O271" s="2"/>
       <c r="P271" s="2"/>
@@ -45148,7 +45144,7 @@
         <v>22</v>
       </c>
       <c r="AG271" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AH271" t="s" s="2">
         <v>74</v>
@@ -45165,13 +45161,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -45194,13 +45190,13 @@
         <v>22</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" s="2"/>
@@ -45251,7 +45247,7 @@
         <v>22</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>74</v>
@@ -45268,13 +45264,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
@@ -45297,13 +45293,13 @@
         <v>22</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="O273" s="2"/>
       <c r="P273" s="2"/>
@@ -45354,7 +45350,7 @@
         <v>22</v>
       </c>
       <c r="AG273" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH273" t="s" s="2">
         <v>74</v>
@@ -45371,13 +45367,13 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -45403,10 +45399,10 @@
         <v>76</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" s="2"/>
@@ -45474,13 +45470,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -45503,13 +45499,13 @@
         <v>22</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" s="2"/>
@@ -45560,7 +45556,7 @@
         <v>22</v>
       </c>
       <c r="AG275" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AH275" t="s" s="2">
         <v>74</v>
@@ -45577,13 +45573,13 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -45606,13 +45602,13 @@
         <v>22</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="O276" s="2"/>
       <c r="P276" s="2"/>
@@ -45663,7 +45659,7 @@
         <v>22</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AH276" t="s" s="2">
         <v>74</v>
@@ -45680,13 +45676,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -45709,13 +45705,13 @@
         <v>22</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
@@ -45766,7 +45762,7 @@
         <v>22</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>74</v>
@@ -45783,13 +45779,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -45815,10 +45811,10 @@
         <v>22</v>
       </c>
       <c r="M278" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="N278" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="N278" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="O278" s="2"/>
       <c r="P278" s="2"/>
@@ -45886,13 +45882,13 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -45918,10 +45914,10 @@
         <v>22</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" s="2"/>
@@ -45989,13 +45985,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -46021,10 +46017,10 @@
         <v>76</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" s="2"/>
@@ -46092,13 +46088,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -46178,7 +46174,7 @@
         <v>22</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AH281" t="s" s="2">
         <v>74</v>
@@ -46195,13 +46191,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -46227,10 +46223,10 @@
         <v>76</v>
       </c>
       <c r="M282" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="N282" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="N282" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="O282" s="2"/>
       <c r="P282" s="2"/>
@@ -46298,13 +46294,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -46384,7 +46380,7 @@
         <v>22</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AH283" t="s" s="2">
         <v>74</v>
@@ -46401,13 +46397,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -46430,7 +46426,7 @@
         <v>22</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="M284" t="s" s="2">
         <v>202</v>
@@ -46487,7 +46483,7 @@
         <v>22</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AH284" t="s" s="2">
         <v>74</v>
@@ -46504,13 +46500,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
@@ -46590,7 +46586,7 @@
         <v>22</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AH285" t="s" s="2">
         <v>74</v>
@@ -46607,13 +46603,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -46636,7 +46632,7 @@
         <v>22</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M286" t="s" s="2">
         <v>253</v>
@@ -46693,7 +46689,7 @@
         <v>22</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AH286" t="s" s="2">
         <v>74</v>
@@ -46710,13 +46706,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -46742,10 +46738,10 @@
         <v>76</v>
       </c>
       <c r="M287" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="N287" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="N287" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="O287" s="2"/>
       <c r="P287" s="2"/>
@@ -46813,13 +46809,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -46845,10 +46841,10 @@
         <v>279</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="N288" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" s="2"/>
@@ -46899,7 +46895,7 @@
         <v>22</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AH288" t="s" s="2">
         <v>79</v>
@@ -46916,13 +46912,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -47002,7 +46998,7 @@
         <v>22</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AH289" t="s" s="2">
         <v>74</v>
@@ -47019,13 +47015,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -47105,7 +47101,7 @@
         <v>22</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AH290" t="s" s="2">
         <v>74</v>
@@ -47122,13 +47118,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -47208,7 +47204,7 @@
         <v>22</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>74</v>
@@ -47225,13 +47221,13 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -47311,7 +47307,7 @@
         <v>22</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AH292" t="s" s="2">
         <v>74</v>
@@ -47328,13 +47324,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -47414,7 +47410,7 @@
         <v>22</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>79</v>
@@ -47431,13 +47427,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -47463,10 +47459,10 @@
         <v>76</v>
       </c>
       <c r="M294" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="N294" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="N294" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="O294" s="2"/>
       <c r="P294" s="2"/>
@@ -47534,13 +47530,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -47620,7 +47616,7 @@
         <v>22</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>74</v>
@@ -47637,13 +47633,13 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -47669,10 +47665,10 @@
         <v>22</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
@@ -47740,13 +47736,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
@@ -47772,10 +47768,10 @@
         <v>22</v>
       </c>
       <c r="M297" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N297" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="N297" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="O297" s="2"/>
       <c r="P297" s="2"/>
@@ -47843,13 +47839,13 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
@@ -47875,10 +47871,10 @@
         <v>22</v>
       </c>
       <c r="M298" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="N298" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="N298" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="O298" s="2"/>
       <c r="P298" s="2"/>
@@ -47946,13 +47942,13 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
@@ -47978,10 +47974,10 @@
         <v>22</v>
       </c>
       <c r="M299" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="N299" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="N299" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="O299" s="2"/>
       <c r="P299" s="2"/>
@@ -48049,13 +48045,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -48081,10 +48077,10 @@
         <v>22</v>
       </c>
       <c r="M300" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="N300" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="N300" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="O300" s="2"/>
       <c r="P300" s="2"/>
@@ -48152,13 +48148,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -48184,10 +48180,10 @@
         <v>22</v>
       </c>
       <c r="M301" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="N301" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="N301" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="O301" s="2"/>
       <c r="P301" s="2"/>
@@ -48255,13 +48251,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -48287,10 +48283,10 @@
         <v>22</v>
       </c>
       <c r="M302" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="N302" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="N302" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="O302" s="2"/>
       <c r="P302" s="2"/>
@@ -48358,13 +48354,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -48390,10 +48386,10 @@
         <v>22</v>
       </c>
       <c r="M303" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="N303" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="N303" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" s="2"/>
@@ -48461,13 +48457,13 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
@@ -48493,10 +48489,10 @@
         <v>22</v>
       </c>
       <c r="M304" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="N304" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="N304" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
@@ -48564,13 +48560,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -48596,10 +48592,10 @@
         <v>22</v>
       </c>
       <c r="M305" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="N305" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="N305" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
@@ -48667,13 +48663,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
@@ -48699,10 +48695,10 @@
         <v>22</v>
       </c>
       <c r="M306" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="N306" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="N306" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="O306" s="2"/>
       <c r="P306" s="2"/>
@@ -48770,13 +48766,13 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -48802,10 +48798,10 @@
         <v>22</v>
       </c>
       <c r="M307" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="N307" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="N307" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="O307" s="2"/>
       <c r="P307" s="2"/>
@@ -48873,13 +48869,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -48905,10 +48901,10 @@
         <v>76</v>
       </c>
       <c r="M308" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="N308" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="N308" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="O308" s="2"/>
       <c r="P308" s="2"/>
@@ -48976,13 +48972,13 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -49062,7 +49058,7 @@
         <v>22</v>
       </c>
       <c r="AG309" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH309" t="s" s="2">
         <v>74</v>
@@ -49079,13 +49075,13 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -49165,7 +49161,7 @@
         <v>22</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>74</v>
@@ -49182,13 +49178,13 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -49268,7 +49264,7 @@
         <v>22</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>74</v>
@@ -49285,13 +49281,13 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -49317,10 +49313,10 @@
         <v>22</v>
       </c>
       <c r="M312" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="N312" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="N312" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" s="2"/>
